--- a/tests/agent_contract/data/S9_multi_filter.xlsx
+++ b/tests/agent_contract/data/S9_multi_filter.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,43 +413,65 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>产品ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>产品ID</t>
+          <t>P10001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
+          <t>产品A</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3956</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>区域</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P10001</t>
+          <t>P10002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -462,7 +480,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2502</v>
+        <v>2118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -478,7 +496,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P10002</t>
+          <t>P10003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,7 +505,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1864</v>
+        <v>3695</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -503,7 +521,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P10003</t>
+          <t>P10004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -512,7 +530,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1969</v>
+        <v>2724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -528,7 +546,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P10004</t>
+          <t>P10005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -537,7 +555,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2581</v>
+        <v>1993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -553,7 +571,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P10005</t>
+          <t>P10006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -562,7 +580,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3229</v>
+        <v>3572</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -578,7 +596,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P10006</t>
+          <t>P10007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -587,7 +605,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3537</v>
+        <v>2950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -603,7 +621,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P10007</t>
+          <t>P10008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -612,7 +630,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3370</v>
+        <v>3557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -628,7 +646,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P10008</t>
+          <t>P10009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -637,7 +655,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2206</v>
+        <v>1921</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -653,7 +671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P10009</t>
+          <t>P10010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -662,7 +680,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2194</v>
+        <v>1846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -678,7 +696,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P10010</t>
+          <t>P10011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -687,7 +705,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2547</v>
+        <v>2247</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -703,7 +721,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P10011</t>
+          <t>P10012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -712,7 +730,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19001</v>
+        <v>2594</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -728,7 +746,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P10012</t>
+          <t>P10013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -737,11 +755,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1501</v>
+        <v>1828</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -753,7 +771,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P10013</t>
+          <t>P10014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -762,7 +780,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1433</v>
+        <v>3138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -771,14 +789,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P10014</t>
+          <t>P10015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -787,7 +805,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1595</v>
+        <v>6861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -796,14 +814,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P10015</t>
+          <t>P10016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -812,11 +830,11 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1437</v>
+        <v>4527</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -828,7 +846,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P10016</t>
+          <t>P10017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -837,23 +855,23 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1688</v>
+        <v>2168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P10017</t>
+          <t>P10018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -862,7 +880,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4600</v>
+        <v>2743</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -878,7 +896,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P10018</t>
+          <t>P10019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -887,7 +905,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4997</v>
+        <v>2987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -903,7 +921,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P10019</t>
+          <t>P10020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -912,7 +930,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1950</v>
+        <v>4373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -921,14 +939,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P10020</t>
+          <t>P10021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -937,36 +955,36 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3513</v>
+        <v>3519</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P10021</t>
+          <t>P10022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>产品B</t>
+          <t>产品A</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2632</v>
+        <v>3879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>停售</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -978,7 +996,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P10022</t>
+          <t>P10023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -987,7 +1005,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3495</v>
+        <v>3377</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1003,7 +1021,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P10023</t>
+          <t>P10024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1012,7 +1030,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3230</v>
+        <v>3723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1028,7 +1046,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P10024</t>
+          <t>P10025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1037,7 +1055,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2394</v>
+        <v>3882</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1053,7 +1071,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P10025</t>
+          <t>P10026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1062,7 +1080,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3619</v>
+        <v>3302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1078,7 +1096,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P10026</t>
+          <t>P10027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1087,7 +1105,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3482</v>
+        <v>3325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1103,7 +1121,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P10027</t>
+          <t>P10028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1112,7 +1130,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2276</v>
+        <v>3333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1128,7 +1146,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P10028</t>
+          <t>P10029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1137,7 +1155,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3715</v>
+        <v>1712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1153,7 +1171,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P10029</t>
+          <t>P10030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1162,7 +1180,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1583</v>
+        <v>3994</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1178,7 +1196,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>P10030</t>
+          <t>P10031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1187,7 +1205,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3473</v>
+        <v>3661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1203,7 +1221,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P10031</t>
+          <t>P10032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1212,7 +1230,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1793</v>
+        <v>3171</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1228,7 +1246,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P10032</t>
+          <t>P10033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1237,7 +1255,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2842</v>
+        <v>4520</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1253,7 +1271,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P10033</t>
+          <t>P10034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1262,11 +1280,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1835</v>
+        <v>3820</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>停售</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1278,7 +1296,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P10034</t>
+          <t>P10035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1287,11 +1305,11 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1631</v>
+        <v>3569</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>停售</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1303,7 +1321,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P10035</t>
+          <t>P10036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1312,7 +1330,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1228</v>
+        <v>1796</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1321,14 +1339,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>P10036</t>
+          <t>P10037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1337,7 +1355,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3629</v>
+        <v>3133</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1346,14 +1364,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>P10037</t>
+          <t>P10038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1362,7 +1380,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3746</v>
+        <v>3108</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1378,7 +1396,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>P10038</t>
+          <t>P10039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1387,23 +1405,23 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2675</v>
+        <v>4849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>P10039</t>
+          <t>P10040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1412,11 +1430,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4316</v>
+        <v>2073</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1428,7 +1446,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>P10040</t>
+          <t>P10041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1437,61 +1455,61 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4505</v>
+        <v>1937</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>停售</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P10041</t>
+          <t>P10042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>产品B</t>
+          <t>产品C</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2594</v>
+        <v>3523</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>P10042</t>
+          <t>P10043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>产品B</t>
+          <t>产品C</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4341</v>
+        <v>3414</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1503,16 +1521,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>P10043</t>
+          <t>P10044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>产品B</t>
+          <t>产品C</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4668</v>
+        <v>3430</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1521,23 +1539,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>P10044</t>
+          <t>P10045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>产品B</t>
+          <t>产品C</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2275</v>
+        <v>3536</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1546,14 +1564,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>P10045</t>
+          <t>P10046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1562,7 +1580,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3323</v>
+        <v>3968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1578,7 +1596,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>P10046</t>
+          <t>P10047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1587,7 +1605,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1803</v>
+        <v>3516</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1603,7 +1621,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>P10047</t>
+          <t>P10048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1612,7 +1630,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2877</v>
+        <v>2101</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1628,7 +1646,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>P10048</t>
+          <t>P10049</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1637,7 +1655,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3892</v>
+        <v>2281</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1653,7 +1671,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>P10049</t>
+          <t>P10050</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1662,7 +1680,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2406</v>
+        <v>2284</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1678,7 +1696,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>P10050</t>
+          <t>P10051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1687,7 +1705,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2526</v>
+        <v>2149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1703,7 +1721,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>P10051</t>
+          <t>P10052</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1712,7 +1730,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2484</v>
+        <v>1798</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1728,7 +1746,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P10052</t>
+          <t>P10053</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1737,11 +1755,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2853</v>
+        <v>2201</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>停售</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1753,7 +1771,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>P10053</t>
+          <t>P10054</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1762,7 +1780,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9836</v>
+        <v>4149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1771,14 +1789,14 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>P10054</t>
+          <t>P10055</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1787,7 +1805,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2316</v>
+        <v>1770</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1796,14 +1814,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>P10055</t>
+          <t>P10056</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1812,7 +1830,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2779</v>
+        <v>3260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1828,7 +1846,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>P10056</t>
+          <t>P10057</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1837,11 +1855,11 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3034</v>
+        <v>1261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>停售</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1853,7 +1871,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>P10057</t>
+          <t>P10058</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1862,32 +1880,32 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3640</v>
+        <v>2860</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>停售</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>P10058</t>
+          <t>P10059</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1072</v>
+        <v>1904</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1896,23 +1914,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>P10059</t>
+          <t>P10060</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1624</v>
+        <v>2327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1921,27 +1939,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>P10060</t>
+          <t>P10061</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1345</v>
+        <v>3096</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1953,45 +1971,45 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>P10061</t>
+          <t>P10062</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2384</v>
+        <v>2337</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>P10062</t>
+          <t>P10063</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1351</v>
+        <v>2687</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2003,16 +2021,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>P10063</t>
+          <t>P10064</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3420</v>
+        <v>2076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2021,14 +2039,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>P10064</t>
+          <t>P10065</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2037,7 +2055,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3647</v>
+        <v>1518</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2053,7 +2071,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>P10065</t>
+          <t>P10066</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2062,7 +2080,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3925</v>
+        <v>1541</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2078,7 +2096,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>P10066</t>
+          <t>P10067</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2087,7 +2105,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3672</v>
+        <v>1510</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2103,7 +2121,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>P10067</t>
+          <t>P10068</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2112,7 +2130,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3351</v>
+        <v>1500</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2128,7 +2146,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>P10068</t>
+          <t>P10069</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2137,7 +2155,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3595</v>
+        <v>1503</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2153,7 +2171,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>P10069</t>
+          <t>P10070</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2162,7 +2180,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2455</v>
+        <v>1501</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2178,7 +2196,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>P10070</t>
+          <t>P10071</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2187,7 +2205,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3752</v>
+        <v>1500</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2203,7 +2221,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>P10071</t>
+          <t>P10072</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2212,7 +2230,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3603</v>
+        <v>1500</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2228,7 +2246,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>P10072</t>
+          <t>P10073</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2237,11 +2255,11 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2413</v>
+        <v>1500</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2253,7 +2271,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>P10073</t>
+          <t>P10074</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2262,7 +2280,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2945</v>
+        <v>1764</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2271,14 +2289,14 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>P10074</t>
+          <t>P10075</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2287,23 +2305,23 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1385</v>
+        <v>1343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>P10075</t>
+          <t>P10076</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2312,7 +2330,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4282</v>
+        <v>4254</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2328,7 +2346,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>P10076</t>
+          <t>P10077</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2337,7 +2355,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3717</v>
+        <v>3603</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2346,14 +2364,14 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>P10077</t>
+          <t>P10078</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2362,7 +2380,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4647</v>
+        <v>4042</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2371,77 +2389,77 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>P10078</t>
+          <t>P10079</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>产品E</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3012</v>
+        <v>2699</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>停售</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>P10079</t>
+          <t>P10080</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>产品E</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2209</v>
+        <v>2791</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>停售</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>P10080</t>
+          <t>P10081</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>产品E</t>
+          <t>产品D</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1714</v>
+        <v>2982</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>停售</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2453,7 +2471,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>P10081</t>
+          <t>P10082</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2462,7 +2480,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1508</v>
+        <v>2759</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2478,7 +2496,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>P10082</t>
+          <t>P10083</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2487,7 +2505,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1552</v>
+        <v>2242</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2503,7 +2521,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>P10083</t>
+          <t>P10084</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2512,7 +2530,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1502</v>
+        <v>2932</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2528,7 +2546,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>P10084</t>
+          <t>P10085</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2537,7 +2555,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1503</v>
+        <v>1733</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2553,7 +2571,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>P10085</t>
+          <t>P10086</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2562,7 +2580,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1500</v>
+        <v>1653</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2578,7 +2596,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>P10086</t>
+          <t>P10087</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2587,7 +2605,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1500</v>
+        <v>1562</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2603,7 +2621,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>P10087</t>
+          <t>P10088</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2612,7 +2630,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1500</v>
+        <v>1605</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2628,7 +2646,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>P10088</t>
+          <t>P10089</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2637,7 +2655,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1500</v>
+        <v>1513</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2653,7 +2671,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>P10089</t>
+          <t>P10090</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2662,7 +2680,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2678,7 +2696,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>P10090</t>
+          <t>P10091</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2703,7 +2721,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>P10091</t>
+          <t>P10092</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2712,23 +2730,23 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2552</v>
+        <v>1500</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>P10092</t>
+          <t>P10093</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2737,11 +2755,11 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3103</v>
+        <v>1500</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -2753,7 +2771,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>P10093</t>
+          <t>P10094</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2762,7 +2780,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3057</v>
+        <v>1673</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2771,14 +2789,14 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>P10094</t>
+          <t>P10095</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2787,7 +2805,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4896</v>
+        <v>1249</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2803,7 +2821,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>P10095</t>
+          <t>P10096</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2812,11 +2830,11 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3051</v>
+        <v>3716</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2828,7 +2846,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>P10096</t>
+          <t>P10097</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2837,7 +2855,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4237</v>
+        <v>4690</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2846,14 +2864,14 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>P10097</t>
+          <t>P10098</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2862,7 +2880,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2502</v>
+        <v>3477</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2871,82 +2889,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>P10098</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>产品E</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>2964</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>停售</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>P10099</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>产品E</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>2193</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>停售</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>P10100</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>产品E</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>4084</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
     </row>
